--- a/sheets/민요/검수/봄철나비.xlsx
+++ b/sheets/민요/검수/봄철나비.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="227">
   <si>
     <t xml:space="preserve">거스러미 돈돈날이</t>
   </si>
@@ -739,31 +739,9 @@
 △</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">南
+–
+南</t>
   </si>
   <si>
     <t xml:space="preserve">춤
@@ -775,161 +753,45 @@
 리</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">꽃
-을</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">추
-노</t>
-  </si>
-  <si>
-    <t xml:space="preserve">꺽
-는</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">따
-라</t>
-  </si>
-  <si>
-    <t xml:space="preserve">다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">–
-–
-△</t>
-  </si>
-  <si>
-    <t xml:space="preserve">潢
-無
-–</t>
-  </si>
-  <si>
-    <t xml:space="preserve">潢
-–
-潢</t>
-  </si>
-  <si>
-    <t xml:space="preserve">우
-리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無
-–
-無</t>
-  </si>
-  <si>
-    <t xml:space="preserve">㴌
-–
-㴌</t>
-  </si>
-  <si>
-    <t xml:space="preserve">북
-청</t>
-  </si>
-  <si>
-    <t xml:space="preserve">南
-–
-仲</t>
-  </si>
-  <si>
-    <t xml:space="preserve">南
-–
-南</t>
-  </si>
-  <si>
     <t xml:space="preserve">潢
 –
 㴌</t>
   </si>
   <si>
-    <t xml:space="preserve">오
-월</t>
+    <t xml:space="preserve">꽃
+을</t>
+  </si>
+  <si>
+    <t xml:space="preserve">추
+노</t>
+  </si>
+  <si>
+    <t xml:space="preserve">꺽
+는</t>
   </si>
   <si>
     <t xml:space="preserve">潢
 –
 無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">따
+라</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">우
+리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">북
+청</t>
+  </si>
+  <si>
+    <t xml:space="preserve">오
+월</t>
   </si>
   <si>
     <t xml:space="preserve">단
@@ -943,7 +805,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -990,11 +852,6 @@
       <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1093,7 +950,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1146,10 +1003,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1176,10 +1029,6 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1662,13 +1511,13 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|潢</t>
+          <t xml:space="preserve">潢|–|潢</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 潢</t>
         </is>
       </c>
@@ -1700,13 +1549,13 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|―|㴌</t>
+          <t xml:space="preserve">㴌|–|㴌</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―
+–
 㴌</t>
         </is>
       </c>
@@ -1773,13 +1622,13 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―|△</t>
+          <t xml:space="preserve">–|–|△</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―
+          <t xml:space="preserve">–
+–
 △</t>
         </is>
       </c>
@@ -1806,13 +1655,13 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|㴌</t>
+          <t xml:space="preserve">潢|–|㴌</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 㴌</t>
         </is>
       </c>
@@ -1844,13 +1693,13 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|無</t>
+          <t xml:space="preserve">潢|–|無</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 無</t>
         </is>
       </c>
@@ -1917,13 +1766,13 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―|△</t>
+          <t xml:space="preserve">–|–|△</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―
+          <t xml:space="preserve">–
+–
 △</t>
         </is>
       </c>
@@ -1950,14 +1799,14 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無|―</t>
+          <t xml:space="preserve">潢|無|–</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1988,13 +1837,13 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|無</t>
+          <t xml:space="preserve">無|–|無</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 無</t>
         </is>
       </c>
@@ -2063,13 +1912,13 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|仲</t>
+          <t xml:space="preserve">南|–|仲</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 仲</t>
         </is>
       </c>
@@ -2101,13 +1950,13 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|南</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -2140,13 +1989,13 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|仲</t>
+          <t xml:space="preserve">南|–|仲</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 仲</t>
         </is>
       </c>
@@ -2213,13 +2062,13 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―|△</t>
+          <t xml:space="preserve">–|–|△</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―
+          <t xml:space="preserve">–
+–
 △</t>
         </is>
       </c>
@@ -2246,14 +2095,14 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無|―</t>
+          <t xml:space="preserve">潢|無|–</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -2284,13 +2133,13 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|無</t>
+          <t xml:space="preserve">無|–|無</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 無</t>
         </is>
       </c>
@@ -2359,13 +2208,13 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|仲</t>
+          <t xml:space="preserve">南|–|仲</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 仲</t>
         </is>
       </c>
@@ -2397,13 +2246,13 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|南</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -2436,13 +2285,13 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|仲</t>
+          <t xml:space="preserve">南|–|仲</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 仲</t>
         </is>
       </c>
@@ -2509,13 +2358,13 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―|△</t>
+          <t xml:space="preserve">–|–|△</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―
+          <t xml:space="preserve">–
+–
 △</t>
         </is>
       </c>
@@ -2542,13 +2391,13 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|潢</t>
+          <t xml:space="preserve">潢|–|潢</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 潢</t>
         </is>
       </c>
@@ -2580,13 +2429,13 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|―|㴌</t>
+          <t xml:space="preserve">㴌|–|㴌</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―
+–
 㴌</t>
         </is>
       </c>
@@ -2653,13 +2502,13 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|㴌</t>
+          <t xml:space="preserve">潢|–|㴌</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 㴌</t>
         </is>
       </c>
@@ -2691,13 +2540,13 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|無</t>
+          <t xml:space="preserve">潢|–|無</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 無</t>
         </is>
       </c>
@@ -2764,13 +2613,13 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―|△</t>
+          <t xml:space="preserve">–|–|△</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―
+          <t xml:space="preserve">–
+–
 △</t>
         </is>
       </c>
@@ -2797,14 +2646,14 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無|―</t>
+          <t xml:space="preserve">潢|無|–</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -2835,13 +2684,13 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|無</t>
+          <t xml:space="preserve">無|–|無</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 無</t>
         </is>
       </c>
@@ -2911,13 +2760,13 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|仲</t>
+          <t xml:space="preserve">南|–|仲</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 仲</t>
         </is>
       </c>
@@ -2949,13 +2798,13 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|南</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -2987,13 +2836,13 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|仲</t>
+          <t xml:space="preserve">南|–|仲</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 仲</t>
         </is>
       </c>
@@ -3060,13 +2909,13 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―|△</t>
+          <t xml:space="preserve">–|–|△</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―
+          <t xml:space="preserve">–
+–
 △</t>
         </is>
       </c>
@@ -3093,14 +2942,14 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無|―</t>
+          <t xml:space="preserve">潢|無|–</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -3131,13 +2980,13 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|無</t>
+          <t xml:space="preserve">無|–|無</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 無</t>
         </is>
       </c>
@@ -3207,13 +3056,13 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|仲</t>
+          <t xml:space="preserve">南|–|仲</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 仲</t>
         </is>
       </c>
@@ -3245,13 +3094,13 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|南</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -3283,13 +3132,13 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|仲</t>
+          <t xml:space="preserve">南|–|仲</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 仲</t>
         </is>
       </c>
@@ -3356,13 +3205,13 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―|△</t>
+          <t xml:space="preserve">–|–|△</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―
+          <t xml:space="preserve">–
+–
 △</t>
         </is>
       </c>
@@ -3392,577 +3241,577 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="14" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="14" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="14" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="14" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="14" width="6"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="17" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="Q3" s="18" t="s">
+      <c r="Q3" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="R3" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="S3" s="18" t="s">
+      <c r="S3" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="T3" s="17" t="s">
+      <c r="T3" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="U3" s="18" t="s">
+      <c r="U3" s="17" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="17"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="17" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="Q4" s="19" t="s">
+      <c r="Q4" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="R4" s="17" t="s">
+      <c r="R4" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="S4" s="19" t="s">
+      <c r="S4" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="T4" s="17" t="s">
+      <c r="T4" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="U4" s="19" t="s">
+      <c r="U4" s="18" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="17"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="17" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="Q5" s="19" t="s">
+      <c r="Q5" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="R5" s="17" t="s">
+      <c r="R5" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="S5" s="19" t="s">
+      <c r="S5" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="T5" s="17" t="s">
+      <c r="T5" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="U5" s="19" t="s">
+      <c r="U5" s="18" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="17"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="17" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="Q6" s="20" t="s">
+      <c r="Q6" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="R6" s="17" t="s">
+      <c r="R6" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="S6" s="20" t="s">
+      <c r="S6" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="T6" s="17" t="s">
+      <c r="T6" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="U6" s="20"/>
+      <c r="U6" s="19"/>
     </row>
     <row r="7" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="17" t="s">
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="Q7" s="18" t="s">
+      <c r="Q7" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="R7" s="17" t="s">
+      <c r="R7" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="S7" s="18" t="s">
+      <c r="S7" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="T7" s="21" t="s">
+      <c r="T7" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="U7" s="18" t="s">
+      <c r="U7" s="17" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="17"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="17" t="s">
+      <c r="B8" s="16"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q8" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="Q8" s="19" t="s">
+      <c r="R8" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="S8" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="R8" s="17" t="s">
+      <c r="T8" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="U8" s="18" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="16"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q9" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="R9" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="S9" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="T9" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="U9" s="19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="16"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="S10" s="19"/>
+      <c r="T10" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="U10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q11" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="R11" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="S11" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="T11" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="U11" s="17" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="16"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="R12" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="S12" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="T12" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="U12" s="18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="16"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q13" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="R13" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="S13" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="T13" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="U13" s="18" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="16"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q14" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="R14" s="16"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="U14" s="19" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="16"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q15" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="R15" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="S15" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="T15" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="U15" s="17" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="16"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q16" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="S8" s="19" t="s">
+      <c r="R16" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="T8" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="U8" s="19" t="s">
+      <c r="S16" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="T16" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="U16" s="18" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="16"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q17" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="R17" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="S17" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="T17" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="U17" s="18" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="17"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q9" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="R9" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="S9" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="T9" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="U9" s="20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="17"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="S10" s="20"/>
-      <c r="T10" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="U10" s="20"/>
-    </row>
-    <row r="11" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="17"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q11" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="R11" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="S11" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="T11" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="U11" s="18" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="17"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q12" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="R12" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="S12" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="T12" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="U12" s="19" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q13" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="R13" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="S13" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="T13" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="U13" s="19" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="17"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q14" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="R14" s="17"/>
-      <c r="S14" s="20"/>
-      <c r="T14" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="U14" s="20" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="17"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q15" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="R15" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="S15" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="T15" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="U15" s="18" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="17"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q16" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="R16" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="S16" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="U16" s="19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="17"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q17" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="R17" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="S17" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="T17" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="U17" s="19" t="s">
-        <v>223</v>
-      </c>
-    </row>
     <row r="18" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="17"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="S18" s="20"/>
-      <c r="T18" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="U18" s="20"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="S18" s="19"/>
+      <c r="T18" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="U18" s="19"/>
     </row>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/sheets/민요/검수/봄철나비.xlsx
+++ b/sheets/민요/검수/봄철나비.xlsx
@@ -3241,29 +3241,29 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="13" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="13" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="13" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="13" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="13" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="13" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="14" width="6"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="15" t="s">
         <v>194</v>
       </c>
@@ -3287,7 +3287,7 @@
       <c r="T2" s="15"/>
       <c r="U2" s="15"/>
     </row>
-    <row r="3" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="16"/>
       <c r="C3" s="17"/>
       <c r="D3" s="16"/>
@@ -3321,7 +3321,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="16"/>
       <c r="C4" s="18"/>
       <c r="D4" s="16"/>
@@ -3355,7 +3355,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="16"/>
       <c r="C5" s="18"/>
       <c r="D5" s="16"/>
@@ -3389,7 +3389,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="16"/>
       <c r="C6" s="19"/>
       <c r="D6" s="16"/>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="U6" s="19"/>
     </row>
-    <row r="7" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="16"/>
       <c r="C7" s="17"/>
       <c r="D7" s="16"/>
@@ -3455,7 +3455,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="16"/>
       <c r="C8" s="18"/>
       <c r="D8" s="16"/>
@@ -3489,7 +3489,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="16"/>
       <c r="C9" s="18"/>
       <c r="D9" s="16"/>
@@ -3523,7 +3523,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="16"/>
       <c r="C10" s="19"/>
       <c r="D10" s="16"/>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="U10" s="19"/>
     </row>
-    <row r="11" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="16"/>
       <c r="C11" s="17"/>
       <c r="D11" s="16"/>
@@ -3585,7 +3585,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="16"/>
       <c r="C12" s="18"/>
       <c r="D12" s="16"/>
@@ -3619,7 +3619,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="16"/>
       <c r="C13" s="18"/>
       <c r="D13" s="16"/>
@@ -3653,7 +3653,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="16"/>
       <c r="C14" s="19"/>
       <c r="D14" s="16"/>
@@ -3683,7 +3683,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="16"/>
       <c r="C15" s="17"/>
       <c r="D15" s="16"/>
@@ -3717,7 +3717,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="16"/>
       <c r="C16" s="18"/>
       <c r="D16" s="16"/>
@@ -3751,7 +3751,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="16"/>
       <c r="C17" s="18"/>
       <c r="D17" s="16"/>
@@ -3785,7 +3785,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="75.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="16"/>
       <c r="C18" s="19"/>
       <c r="D18" s="16"/>

--- a/sheets/민요/검수/봄철나비.xlsx
+++ b/sheets/민요/검수/봄철나비.xlsx
@@ -805,7 +805,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -849,6 +849,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
@@ -950,7 +956,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1028,6 +1034,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3242,25 +3264,25 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="20" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="20" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="20" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="20" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="20" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="13" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="20" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="13" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="20" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="13" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="20" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="13" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="20" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="13" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="20" width="6"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3289,529 +3311,529 @@
     </row>
     <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="16"/>
-      <c r="C3" s="17"/>
+      <c r="C3" s="21"/>
       <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
+      <c r="E3" s="21"/>
       <c r="F3" s="16"/>
-      <c r="G3" s="17"/>
+      <c r="G3" s="21"/>
       <c r="H3" s="16"/>
-      <c r="I3" s="17"/>
+      <c r="I3" s="21"/>
       <c r="J3" s="16"/>
-      <c r="K3" s="17"/>
+      <c r="K3" s="21"/>
       <c r="L3" s="16"/>
-      <c r="M3" s="17"/>
+      <c r="M3" s="21"/>
       <c r="N3" s="16"/>
-      <c r="O3" s="17"/>
+      <c r="O3" s="21"/>
       <c r="P3" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="21" t="s">
         <v>196</v>
       </c>
       <c r="R3" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="21" t="s">
         <v>197</v>
       </c>
       <c r="T3" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="U3" s="17" t="s">
+      <c r="U3" s="21" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="16"/>
-      <c r="C4" s="18"/>
+      <c r="C4" s="22"/>
       <c r="D4" s="16"/>
-      <c r="E4" s="18"/>
+      <c r="E4" s="22"/>
       <c r="F4" s="16"/>
-      <c r="G4" s="18"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="16"/>
-      <c r="I4" s="18"/>
+      <c r="I4" s="22"/>
       <c r="J4" s="16"/>
-      <c r="K4" s="18"/>
+      <c r="K4" s="22"/>
       <c r="L4" s="16"/>
-      <c r="M4" s="18"/>
+      <c r="M4" s="22"/>
       <c r="N4" s="16"/>
-      <c r="O4" s="18"/>
+      <c r="O4" s="22"/>
       <c r="P4" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="Q4" s="18" t="s">
+      <c r="Q4" s="22" t="s">
         <v>201</v>
       </c>
       <c r="R4" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="S4" s="18" t="s">
+      <c r="S4" s="22" t="s">
         <v>202</v>
       </c>
       <c r="T4" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="U4" s="18" t="s">
+      <c r="U4" s="22" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="16"/>
-      <c r="C5" s="18"/>
+      <c r="C5" s="22"/>
       <c r="D5" s="16"/>
-      <c r="E5" s="18"/>
+      <c r="E5" s="22"/>
       <c r="F5" s="16"/>
-      <c r="G5" s="18"/>
+      <c r="G5" s="22"/>
       <c r="H5" s="16"/>
-      <c r="I5" s="18"/>
+      <c r="I5" s="22"/>
       <c r="J5" s="16"/>
-      <c r="K5" s="18"/>
+      <c r="K5" s="22"/>
       <c r="L5" s="16"/>
-      <c r="M5" s="18"/>
+      <c r="M5" s="22"/>
       <c r="N5" s="16"/>
-      <c r="O5" s="18"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="Q5" s="18" t="s">
+      <c r="Q5" s="22" t="s">
         <v>206</v>
       </c>
       <c r="R5" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="S5" s="18" t="s">
+      <c r="S5" s="22" t="s">
         <v>207</v>
       </c>
       <c r="T5" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="U5" s="18" t="s">
+      <c r="U5" s="22" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="16"/>
-      <c r="C6" s="19"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="16"/>
-      <c r="E6" s="19"/>
+      <c r="E6" s="23"/>
       <c r="F6" s="16"/>
-      <c r="G6" s="19"/>
+      <c r="G6" s="23"/>
       <c r="H6" s="16"/>
-      <c r="I6" s="19"/>
+      <c r="I6" s="23"/>
       <c r="J6" s="16"/>
-      <c r="K6" s="19"/>
+      <c r="K6" s="23"/>
       <c r="L6" s="16"/>
-      <c r="M6" s="18"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="16"/>
-      <c r="O6" s="19"/>
+      <c r="O6" s="23"/>
       <c r="P6" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="Q6" s="19" t="s">
+      <c r="Q6" s="23" t="s">
         <v>210</v>
       </c>
       <c r="R6" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="S6" s="19" t="s">
+      <c r="S6" s="23" t="s">
         <v>211</v>
       </c>
       <c r="T6" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="U6" s="19"/>
+      <c r="U6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
+      <c r="C7" s="21"/>
       <c r="D7" s="16"/>
-      <c r="E7" s="17"/>
+      <c r="E7" s="21"/>
       <c r="F7" s="16"/>
-      <c r="G7" s="17"/>
+      <c r="G7" s="21"/>
       <c r="H7" s="16"/>
-      <c r="I7" s="17"/>
+      <c r="I7" s="21"/>
       <c r="J7" s="16"/>
-      <c r="K7" s="17"/>
+      <c r="K7" s="21"/>
       <c r="L7" s="16"/>
-      <c r="M7" s="17"/>
+      <c r="M7" s="21"/>
       <c r="N7" s="16"/>
-      <c r="O7" s="17"/>
+      <c r="O7" s="21"/>
       <c r="P7" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="Q7" s="17" t="s">
+      <c r="Q7" s="21" t="s">
         <v>214</v>
       </c>
       <c r="R7" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="S7" s="17" t="s">
+      <c r="S7" s="21" t="s">
         <v>215</v>
       </c>
       <c r="T7" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="U7" s="17" t="s">
+      <c r="U7" s="21" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="16"/>
-      <c r="C8" s="18"/>
+      <c r="C8" s="22"/>
       <c r="D8" s="16"/>
-      <c r="E8" s="18"/>
+      <c r="E8" s="22"/>
       <c r="F8" s="16"/>
-      <c r="G8" s="18"/>
+      <c r="G8" s="22"/>
       <c r="H8" s="16"/>
-      <c r="I8" s="18"/>
+      <c r="I8" s="22"/>
       <c r="J8" s="16"/>
-      <c r="K8" s="18"/>
+      <c r="K8" s="22"/>
       <c r="L8" s="16"/>
-      <c r="M8" s="18"/>
+      <c r="M8" s="22"/>
       <c r="N8" s="16"/>
-      <c r="O8" s="18"/>
+      <c r="O8" s="22"/>
       <c r="P8" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="Q8" s="18" t="s">
+      <c r="Q8" s="22" t="s">
         <v>218</v>
       </c>
       <c r="R8" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="S8" s="18" t="s">
+      <c r="S8" s="22" t="s">
         <v>219</v>
       </c>
       <c r="T8" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="U8" s="18" t="s">
+      <c r="U8" s="22" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="16"/>
-      <c r="C9" s="18"/>
+      <c r="C9" s="22"/>
       <c r="D9" s="16"/>
-      <c r="E9" s="18"/>
+      <c r="E9" s="22"/>
       <c r="F9" s="16"/>
-      <c r="G9" s="18"/>
+      <c r="G9" s="22"/>
       <c r="H9" s="16"/>
-      <c r="I9" s="18"/>
+      <c r="I9" s="22"/>
       <c r="J9" s="16"/>
-      <c r="K9" s="18"/>
+      <c r="K9" s="22"/>
       <c r="L9" s="16"/>
-      <c r="M9" s="19"/>
+      <c r="M9" s="23"/>
       <c r="N9" s="16"/>
-      <c r="O9" s="19"/>
+      <c r="O9" s="23"/>
       <c r="P9" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="Q9" s="19" t="s">
+      <c r="Q9" s="23" t="s">
         <v>146</v>
       </c>
       <c r="R9" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="S9" s="19" t="s">
+      <c r="S9" s="23" t="s">
         <v>222</v>
       </c>
       <c r="T9" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="U9" s="19" t="s">
+      <c r="U9" s="23" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="16"/>
-      <c r="C10" s="19"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="16"/>
-      <c r="E10" s="19"/>
+      <c r="E10" s="23"/>
       <c r="F10" s="16"/>
-      <c r="G10" s="19"/>
+      <c r="G10" s="23"/>
       <c r="H10" s="16"/>
-      <c r="I10" s="19"/>
+      <c r="I10" s="23"/>
       <c r="J10" s="16"/>
-      <c r="K10" s="19"/>
+      <c r="K10" s="23"/>
       <c r="L10" s="16"/>
-      <c r="M10" s="19"/>
+      <c r="M10" s="23"/>
       <c r="N10" s="16"/>
-      <c r="O10" s="19"/>
+      <c r="O10" s="23"/>
       <c r="P10" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="Q10" s="19"/>
+      <c r="Q10" s="23"/>
       <c r="R10" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="S10" s="19"/>
+      <c r="S10" s="23"/>
       <c r="T10" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="U10" s="19"/>
+      <c r="U10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="16"/>
-      <c r="C11" s="17"/>
+      <c r="C11" s="21"/>
       <c r="D11" s="16"/>
-      <c r="E11" s="17"/>
+      <c r="E11" s="21"/>
       <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
+      <c r="G11" s="21"/>
       <c r="H11" s="16"/>
-      <c r="I11" s="17"/>
+      <c r="I11" s="21"/>
       <c r="J11" s="16"/>
-      <c r="K11" s="17"/>
+      <c r="K11" s="21"/>
       <c r="L11" s="16"/>
-      <c r="M11" s="17"/>
+      <c r="M11" s="21"/>
       <c r="N11" s="16"/>
-      <c r="O11" s="17"/>
+      <c r="O11" s="21"/>
       <c r="P11" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="Q11" s="17" t="s">
+      <c r="Q11" s="21" t="s">
         <v>196</v>
       </c>
       <c r="R11" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="S11" s="17" t="s">
+      <c r="S11" s="21" t="s">
         <v>223</v>
       </c>
       <c r="T11" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="U11" s="17" t="s">
+      <c r="U11" s="21" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="16"/>
-      <c r="C12" s="18"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="16"/>
-      <c r="E12" s="18"/>
+      <c r="E12" s="22"/>
       <c r="F12" s="16"/>
-      <c r="G12" s="18"/>
+      <c r="G12" s="22"/>
       <c r="H12" s="16"/>
-      <c r="I12" s="18"/>
+      <c r="I12" s="22"/>
       <c r="J12" s="16"/>
-      <c r="K12" s="18"/>
+      <c r="K12" s="22"/>
       <c r="L12" s="16"/>
-      <c r="M12" s="18"/>
+      <c r="M12" s="22"/>
       <c r="N12" s="16"/>
-      <c r="O12" s="18"/>
+      <c r="O12" s="22"/>
       <c r="P12" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="Q12" s="18" t="s">
+      <c r="Q12" s="22" t="s">
         <v>201</v>
       </c>
       <c r="R12" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="S12" s="18" t="s">
+      <c r="S12" s="22" t="s">
         <v>224</v>
       </c>
       <c r="T12" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="U12" s="18" t="s">
+      <c r="U12" s="22" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="16"/>
-      <c r="C13" s="18"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="16"/>
-      <c r="E13" s="18"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="16"/>
-      <c r="G13" s="18"/>
+      <c r="G13" s="22"/>
       <c r="H13" s="16"/>
-      <c r="I13" s="18"/>
+      <c r="I13" s="22"/>
       <c r="J13" s="16"/>
-      <c r="K13" s="18"/>
+      <c r="K13" s="22"/>
       <c r="L13" s="16"/>
-      <c r="M13" s="18"/>
+      <c r="M13" s="22"/>
       <c r="N13" s="16"/>
-      <c r="O13" s="18"/>
+      <c r="O13" s="22"/>
       <c r="P13" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="Q13" s="18" t="s">
+      <c r="Q13" s="22" t="s">
         <v>206</v>
       </c>
       <c r="R13" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="S13" s="18" t="s">
+      <c r="S13" s="22" t="s">
         <v>165</v>
       </c>
       <c r="T13" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="U13" s="18" t="s">
+      <c r="U13" s="22" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="16"/>
-      <c r="C14" s="19"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="16"/>
-      <c r="E14" s="19"/>
+      <c r="E14" s="23"/>
       <c r="F14" s="16"/>
-      <c r="G14" s="19"/>
+      <c r="G14" s="23"/>
       <c r="H14" s="16"/>
-      <c r="I14" s="19"/>
+      <c r="I14" s="23"/>
       <c r="J14" s="16"/>
-      <c r="K14" s="18"/>
+      <c r="K14" s="22"/>
       <c r="L14" s="16"/>
-      <c r="M14" s="19"/>
+      <c r="M14" s="23"/>
       <c r="N14" s="16"/>
-      <c r="O14" s="19"/>
+      <c r="O14" s="23"/>
       <c r="P14" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="Q14" s="19" t="s">
+      <c r="Q14" s="23" t="s">
         <v>210</v>
       </c>
       <c r="R14" s="16"/>
-      <c r="S14" s="19"/>
+      <c r="S14" s="23"/>
       <c r="T14" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="U14" s="19" t="s">
+      <c r="U14" s="23" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="16"/>
-      <c r="C15" s="17"/>
+      <c r="C15" s="21"/>
       <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
+      <c r="E15" s="21"/>
       <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
+      <c r="G15" s="21"/>
       <c r="H15" s="16"/>
-      <c r="I15" s="17"/>
+      <c r="I15" s="21"/>
       <c r="J15" s="16"/>
-      <c r="K15" s="17"/>
+      <c r="K15" s="21"/>
       <c r="L15" s="16"/>
-      <c r="M15" s="17"/>
+      <c r="M15" s="21"/>
       <c r="N15" s="16"/>
-      <c r="O15" s="17"/>
+      <c r="O15" s="21"/>
       <c r="P15" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="Q15" s="17" t="s">
+      <c r="Q15" s="21" t="s">
         <v>214</v>
       </c>
       <c r="R15" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="S15" s="17" t="s">
+      <c r="S15" s="21" t="s">
         <v>225</v>
       </c>
       <c r="T15" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="U15" s="17" t="s">
+      <c r="U15" s="21" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="16"/>
-      <c r="C16" s="18"/>
+      <c r="C16" s="22"/>
       <c r="D16" s="16"/>
-      <c r="E16" s="18"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="16"/>
-      <c r="G16" s="18"/>
+      <c r="G16" s="22"/>
       <c r="H16" s="16"/>
-      <c r="I16" s="18"/>
+      <c r="I16" s="22"/>
       <c r="J16" s="16"/>
-      <c r="K16" s="18"/>
+      <c r="K16" s="22"/>
       <c r="L16" s="16"/>
-      <c r="M16" s="18"/>
+      <c r="M16" s="22"/>
       <c r="N16" s="16"/>
-      <c r="O16" s="18"/>
+      <c r="O16" s="22"/>
       <c r="P16" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="Q16" s="18" t="s">
+      <c r="Q16" s="22" t="s">
         <v>218</v>
       </c>
       <c r="R16" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="S16" s="18" t="s">
+      <c r="S16" s="22" t="s">
         <v>226</v>
       </c>
       <c r="T16" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="U16" s="18" t="s">
+      <c r="U16" s="22" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="16"/>
-      <c r="C17" s="18"/>
+      <c r="C17" s="22"/>
       <c r="D17" s="16"/>
-      <c r="E17" s="18"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="16"/>
-      <c r="G17" s="18"/>
+      <c r="G17" s="22"/>
       <c r="H17" s="16"/>
-      <c r="I17" s="18"/>
+      <c r="I17" s="22"/>
       <c r="J17" s="16"/>
-      <c r="K17" s="19"/>
+      <c r="K17" s="23"/>
       <c r="L17" s="16"/>
-      <c r="M17" s="18"/>
+      <c r="M17" s="22"/>
       <c r="N17" s="16"/>
-      <c r="O17" s="18"/>
+      <c r="O17" s="22"/>
       <c r="P17" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="Q17" s="18" t="s">
+      <c r="Q17" s="22" t="s">
         <v>146</v>
       </c>
       <c r="R17" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="S17" s="18" t="s">
+      <c r="S17" s="22" t="s">
         <v>101</v>
       </c>
       <c r="T17" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="U17" s="18" t="s">
+      <c r="U17" s="22" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="16"/>
-      <c r="C18" s="19"/>
+      <c r="C18" s="23"/>
       <c r="D18" s="16"/>
-      <c r="E18" s="19"/>
+      <c r="E18" s="23"/>
       <c r="F18" s="16"/>
-      <c r="G18" s="19"/>
+      <c r="G18" s="23"/>
       <c r="H18" s="16"/>
-      <c r="I18" s="19"/>
+      <c r="I18" s="23"/>
       <c r="J18" s="16"/>
-      <c r="K18" s="19"/>
+      <c r="K18" s="23"/>
       <c r="L18" s="16"/>
-      <c r="M18" s="19"/>
+      <c r="M18" s="23"/>
       <c r="N18" s="16"/>
-      <c r="O18" s="19"/>
+      <c r="O18" s="23"/>
       <c r="P18" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="Q18" s="19"/>
+      <c r="Q18" s="23"/>
       <c r="R18" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="S18" s="19"/>
+      <c r="S18" s="23"/>
       <c r="T18" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="U18" s="19"/>
+      <c r="U18" s="23"/>
     </row>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/sheets/민요/검수/봄철나비.xlsx
+++ b/sheets/민요/검수/봄철나비.xlsx
@@ -874,10 +874,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/봄철나비.xlsx
+++ b/sheets/민요/검수/봄철나비.xlsx
@@ -3254,7 +3254,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B2:U1048576"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -3282,7 +3282,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="20" width="6"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
       <c r="B2" s="15" t="s">
         <v>194</v>
       </c>
@@ -3306,7 +3307,7 @@
       <c r="T2" s="15"/>
       <c r="U2" s="15"/>
     </row>
-    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B3" s="16"/>
       <c r="C3" s="21"/>
       <c r="D3" s="16"/>
@@ -3340,7 +3341,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B4" s="16"/>
       <c r="C4" s="22"/>
       <c r="D4" s="16"/>
@@ -3374,7 +3375,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B5" s="16"/>
       <c r="C5" s="22"/>
       <c r="D5" s="16"/>
@@ -3408,7 +3409,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B6" s="16"/>
       <c r="C6" s="23"/>
       <c r="D6" s="16"/>
@@ -3440,7 +3441,7 @@
       </c>
       <c r="U6" s="23"/>
     </row>
-    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B7" s="16"/>
       <c r="C7" s="21"/>
       <c r="D7" s="16"/>
@@ -3474,7 +3475,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B8" s="16"/>
       <c r="C8" s="22"/>
       <c r="D8" s="16"/>
@@ -3508,7 +3509,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B9" s="16"/>
       <c r="C9" s="22"/>
       <c r="D9" s="16"/>
@@ -3542,7 +3543,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B10" s="16"/>
       <c r="C10" s="23"/>
       <c r="D10" s="16"/>
@@ -3570,7 +3571,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B11" s="16"/>
       <c r="C11" s="21"/>
       <c r="D11" s="16"/>
@@ -3604,7 +3605,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B12" s="16"/>
       <c r="C12" s="22"/>
       <c r="D12" s="16"/>
@@ -3638,7 +3639,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B13" s="16"/>
       <c r="C13" s="22"/>
       <c r="D13" s="16"/>
@@ -3672,7 +3673,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B14" s="16"/>
       <c r="C14" s="23"/>
       <c r="D14" s="16"/>
@@ -3702,7 +3703,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B15" s="16"/>
       <c r="C15" s="21"/>
       <c r="D15" s="16"/>
@@ -3736,7 +3737,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B16" s="16"/>
       <c r="C16" s="22"/>
       <c r="D16" s="16"/>
@@ -3770,7 +3771,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B17" s="16"/>
       <c r="C17" s="22"/>
       <c r="D17" s="16"/>
@@ -3804,7 +3805,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B18" s="16"/>
       <c r="C18" s="23"/>
       <c r="D18" s="16"/>
@@ -3851,13 +3852,10 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="61" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="18" man="true" max="16383" min="0"/>
-  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/봄철나비.xlsx
+++ b/sheets/민요/검수/봄철나비.xlsx
@@ -3260,30 +3260,30 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="20" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="20" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="20" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="20" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="20" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="20" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="20" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="20" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="20" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="20" width="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="81.63" customHeight="true">
       <c r="B2" s="15" t="s">
         <v>194</v>
       </c>
@@ -3307,7 +3307,7 @@
       <c r="T2" s="15"/>
       <c r="U2" s="15"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B3" s="16"/>
       <c r="C3" s="21"/>
       <c r="D3" s="16"/>
@@ -3341,7 +3341,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B4" s="16"/>
       <c r="C4" s="22"/>
       <c r="D4" s="16"/>
@@ -3375,7 +3375,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B5" s="16"/>
       <c r="C5" s="22"/>
       <c r="D5" s="16"/>
@@ -3409,7 +3409,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B6" s="16"/>
       <c r="C6" s="23"/>
       <c r="D6" s="16"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="U6" s="23"/>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B7" s="16"/>
       <c r="C7" s="21"/>
       <c r="D7" s="16"/>
@@ -3475,7 +3475,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B8" s="16"/>
       <c r="C8" s="22"/>
       <c r="D8" s="16"/>
@@ -3509,7 +3509,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B9" s="16"/>
       <c r="C9" s="22"/>
       <c r="D9" s="16"/>
@@ -3543,7 +3543,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B10" s="16"/>
       <c r="C10" s="23"/>
       <c r="D10" s="16"/>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B11" s="16"/>
       <c r="C11" s="21"/>
       <c r="D11" s="16"/>
@@ -3605,7 +3605,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B12" s="16"/>
       <c r="C12" s="22"/>
       <c r="D12" s="16"/>
@@ -3639,7 +3639,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B13" s="16"/>
       <c r="C13" s="22"/>
       <c r="D13" s="16"/>
@@ -3673,7 +3673,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B14" s="16"/>
       <c r="C14" s="23"/>
       <c r="D14" s="16"/>
@@ -3703,7 +3703,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B15" s="16"/>
       <c r="C15" s="21"/>
       <c r="D15" s="16"/>
@@ -3737,7 +3737,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B16" s="16"/>
       <c r="C16" s="22"/>
       <c r="D16" s="16"/>
@@ -3771,7 +3771,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B17" s="16"/>
       <c r="C17" s="22"/>
       <c r="D17" s="16"/>
@@ -3805,7 +3805,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B18" s="16"/>
       <c r="C18" s="23"/>
       <c r="D18" s="16"/>
@@ -3852,7 +3852,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
